--- a/pages/WR_progressions/Men_TS.xlsx
+++ b/pages/WR_progressions/Men_TS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\WR progressions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5938B131-A2FF-4373-B36D-0D31C843F03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6FFF14-260E-4FEA-AD7E-F75C263FAC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1433" yWindow="975" windowWidth="14999" windowHeight="12000" xr2:uid="{14218ABA-E600-421E-9725-EC4FBE2E4920}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{14218ABA-E600-421E-9725-EC4FBE2E4920}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,10 +83,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,6 +528,34 @@
         <v>43887</v>
       </c>
     </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>41.191000000000003</v>
+      </c>
+      <c r="B8">
+        <v>41.191000000000003</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45510</v>
+      </c>
+      <c r="D8" s="3">
+        <v>45510</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>40.948999999999998</v>
+      </c>
+      <c r="B9">
+        <v>40.948999999999998</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45510</v>
+      </c>
+      <c r="D9" s="3">
+        <v>45510</v>
+      </c>
+    </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="J10" s="1"/>
     </row>
